--- a/source-data/Enerium_Летопись.xlsx
+++ b/source-data/Enerium_Летопись.xlsx
@@ -159,7 +159,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -171,7 +171,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">37d060b787b10e7d — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">d13709a16182db8f — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -250,8 +250,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
